--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.38278023427648</v>
+        <v>8.837201788069928</v>
       </c>
       <c r="D2" t="n">
-        <v>55.97916411682497</v>
+        <v>9.096614168984058</v>
       </c>
       <c r="E2" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.75965639142534</v>
+        <v>4.998444163606617</v>
       </c>
       <c r="D3" t="n">
-        <v>30.4860192674278</v>
+        <v>4.953978130957018</v>
       </c>
       <c r="E3" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.63295254549815</v>
+        <v>5.302854788643449</v>
       </c>
       <c r="D4" t="n">
-        <v>33.08467602107736</v>
+        <v>5.376259853425072</v>
       </c>
       <c r="E4" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F4" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.2572833145432</v>
+        <v>2.64180853861327</v>
       </c>
       <c r="D5" t="n">
-        <v>14.67432707307164</v>
+        <v>2.384578149374142</v>
       </c>
       <c r="E5" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.12624526548704</v>
+        <v>4.733014855641644</v>
       </c>
       <c r="D6" t="n">
-        <v>28.72619487972843</v>
+        <v>4.66800666795587</v>
       </c>
       <c r="E6" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F6" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.36869946495151</v>
+        <v>5.097413663054621</v>
       </c>
       <c r="D7" t="n">
-        <v>30.03818831282307</v>
+        <v>4.881205600833749</v>
       </c>
       <c r="E7" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F7" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.85380110215314</v>
+        <v>3.388742679099885</v>
       </c>
       <c r="D8" t="n">
-        <v>19.65606621210873</v>
+        <v>3.194110759467668</v>
       </c>
       <c r="E8" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F8" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.52722275773374</v>
+        <v>6.260673698131733</v>
       </c>
       <c r="D9" t="n">
-        <v>37.46257161845854</v>
+        <v>6.087667887999513</v>
       </c>
       <c r="E9" t="n">
-        <v>10.75705426404693</v>
+        <v>1.748021317907626</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5709019933687</v>
+        <v>1.880271573922414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
